--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -951,7 +951,7 @@
         <v>456668</v>
       </c>
       <c r="R4" t="n">
-        <v>6956457</v>
+        <v>6956458</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137067742</v>
       </c>
       <c r="B2" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137067746</v>
       </c>
       <c r="B4" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>456668</v>
       </c>
       <c r="R4" t="n">
-        <v>6956458</v>
+        <v>6956457</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1028,7 +1028,7 @@
         <v>137067755</v>
       </c>
       <c r="B5" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137067756</v>
       </c>
       <c r="B6" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137067737</v>
       </c>
       <c r="B9" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137067743</v>
       </c>
       <c r="B10" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>137067753</v>
       </c>
       <c r="B11" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>137067735</v>
       </c>
       <c r="B12" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>137067738</v>
       </c>
       <c r="B13" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>137067752</v>
       </c>
       <c r="B14" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137067760</v>
       </c>
       <c r="B15" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>137067745</v>
       </c>
       <c r="B16" t="n">
-        <v>79159</v>
+        <v>79160</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,32 +913,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137067746</v>
+        <v>137129715</v>
       </c>
       <c r="B4" t="n">
-        <v>80603</v>
+        <v>79240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456668</v>
+        <v>456640</v>
       </c>
       <c r="R4" t="n">
-        <v>6956457</v>
+        <v>6956351</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt på brandmärkt silverstubbe i talldominerad gles skog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,38 +1024,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137067746</t>
+          <t>https://artportalen.se/Sighting/137129715</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137067755</v>
+        <v>137129717</v>
       </c>
       <c r="B5" t="n">
-        <v>80603</v>
+        <v>79240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456652</v>
+        <v>456661</v>
       </c>
       <c r="R5" t="n">
-        <v>6956495</v>
+        <v>6956484</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,12 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Döende sälg</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,16 +1136,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137067755</t>
+          <t>https://artportalen.se/Sighting/137129717</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137067756</v>
+        <v>137067746</v>
       </c>
       <c r="B6" t="n">
-        <v>80609</v>
+        <v>80603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,21 +1153,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456652</v>
+        <v>456668</v>
       </c>
       <c r="R6" t="n">
-        <v>6956495</v>
+        <v>6956458</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,60 +1248,51 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137067756</t>
+          <t>https://artportalen.se/Sighting/137067746</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137067739</v>
+        <v>137067755</v>
       </c>
       <c r="B7" t="n">
-        <v>58169</v>
+        <v>80603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skravelberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456675</v>
+        <v>456652</v>
       </c>
       <c r="R7" t="n">
-        <v>6956401</v>
+        <v>6956495</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1333,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1334,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Döende sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,63 +1365,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137067739</t>
+          <t>https://artportalen.se/Sighting/137067755</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137067750</v>
+        <v>137067756</v>
       </c>
       <c r="B8" t="n">
-        <v>58169</v>
+        <v>80609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skravelberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456663</v>
+        <v>456652</v>
       </c>
       <c r="R8" t="n">
-        <v>6956522</v>
+        <v>6956495</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,54 +1477,63 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137067750</t>
+          <t>https://artportalen.se/Sighting/137067756</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137067737</v>
+        <v>137067739</v>
       </c>
       <c r="B9" t="n">
-        <v>111341</v>
+        <v>58169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220240</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skravelberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456707</v>
+        <v>456675</v>
       </c>
       <c r="R9" t="n">
-        <v>6956394</v>
+        <v>6956401</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1566,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,54 +1598,63 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137067737</t>
+          <t>https://artportalen.se/Sighting/137067739</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137067743</v>
+        <v>137067750</v>
       </c>
       <c r="B10" t="n">
-        <v>111341</v>
+        <v>58169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220240</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skravelberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456686</v>
+        <v>456663</v>
       </c>
       <c r="R10" t="n">
-        <v>6956404</v>
+        <v>6956522</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1693,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,51 +1719,60 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137067743</t>
+          <t>https://artportalen.se/Sighting/137067750</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137067753</v>
+        <v>137067732</v>
       </c>
       <c r="B11" t="n">
-        <v>111341</v>
+        <v>58112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220240</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skravelberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456662</v>
+        <v>456700</v>
       </c>
       <c r="R11" t="n">
-        <v>6956519</v>
+        <v>6956293</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1790,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1814,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lock och förbiflygande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,16 +1845,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137067753</t>
+          <t>https://artportalen.se/Sighting/137067732</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137067735</v>
+        <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>98224</v>
+        <v>111341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,16 +1862,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220240</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1867,13 +1886,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456640</v>
+        <v>456707</v>
       </c>
       <c r="R12" t="n">
-        <v>6956352</v>
+        <v>6956394</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1902,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,16 +1957,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137067735</t>
+          <t>https://artportalen.se/Sighting/137067737</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137067738</v>
+        <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>98224</v>
+        <v>111341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,16 +1974,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220240</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1979,13 +1998,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456692</v>
+        <v>456686</v>
       </c>
       <c r="R13" t="n">
-        <v>6956413</v>
+        <v>6956404</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +2033,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2043,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,7 +2052,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2051,16 +2069,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137067738</t>
+          <t>https://artportalen.se/Sighting/137067743</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137067752</v>
+        <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>98224</v>
+        <v>111341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,16 +2086,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220240</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2095,7 +2113,7 @@
         <v>456662</v>
       </c>
       <c r="R14" t="n">
-        <v>6956520</v>
+        <v>6956519</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2163,13 +2181,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137067752</t>
+          <t>https://artportalen.se/Sighting/137067753</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137067760</v>
+        <v>137067735</v>
       </c>
       <c r="B15" t="n">
         <v>98224</v>
@@ -2204,10 +2222,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456659</v>
+        <v>456640</v>
       </c>
       <c r="R15" t="n">
-        <v>6956484</v>
+        <v>6956352</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2239,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,16 +2293,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137067760</t>
+          <t>https://artportalen.se/Sighting/137067735</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137067745</v>
+        <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>79160</v>
+        <v>98224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2292,21 +2310,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228654</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grå renlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia rangiferina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) F.H.Wigg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,13 +2334,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456684</v>
+        <v>456692</v>
       </c>
       <c r="R16" t="n">
-        <v>6956405</v>
+        <v>6956413</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2351,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,6 +2405,343 @@
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137067738</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137067752</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98224</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skravelberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>456662</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6956520</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137067752</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137067760</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98224</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skravelberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>456659</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6956484</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137067760</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137067745</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79160</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skravelberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>456684</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6956405</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137067745</t>
         </is>
@@ -2409,6 +2764,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137067742</v>
       </c>
       <c r="B2" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137129715</v>
       </c>
       <c r="B4" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>137129717</v>
       </c>
       <c r="B5" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137067746</v>
       </c>
       <c r="B6" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137067755</v>
       </c>
       <c r="B7" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137067756</v>
       </c>
       <c r="B8" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>137067745</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>79162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -1180,7 +1180,7 @@
         <v>456668</v>
       </c>
       <c r="R6" t="n">
-        <v>6956458</v>
+        <v>6956457</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -1180,7 +1180,7 @@
         <v>456668</v>
       </c>
       <c r="R6" t="n">
-        <v>6956457</v>
+        <v>6956458</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1854,7 +1854,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137067742</v>
       </c>
       <c r="B2" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137129715</v>
       </c>
       <c r="B4" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>137129717</v>
       </c>
       <c r="B5" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137067746</v>
       </c>
       <c r="B6" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>456668</v>
       </c>
       <c r="R6" t="n">
-        <v>6956458</v>
+        <v>6956457</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1257,7 +1257,7 @@
         <v>137067755</v>
       </c>
       <c r="B7" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137067756</v>
       </c>
       <c r="B8" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>137067745</v>
       </c>
       <c r="B19" t="n">
-        <v>79162</v>
+        <v>79165</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137067742</v>
       </c>
       <c r="B2" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137129715</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>137129717</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137067746</v>
       </c>
       <c r="B6" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>456668</v>
       </c>
       <c r="R6" t="n">
-        <v>6956457</v>
+        <v>6956458</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1257,7 +1257,7 @@
         <v>137067755</v>
       </c>
       <c r="B7" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137067756</v>
       </c>
       <c r="B8" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137067739</v>
       </c>
       <c r="B9" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>137067750</v>
       </c>
       <c r="B10" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>137067732</v>
       </c>
       <c r="B11" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>137067745</v>
       </c>
       <c r="B19" t="n">
-        <v>79165</v>
+        <v>79178</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137067742</v>
       </c>
       <c r="B2" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137129715</v>
       </c>
       <c r="B4" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>137129717</v>
       </c>
       <c r="B5" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137067746</v>
       </c>
       <c r="B6" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137067755</v>
       </c>
       <c r="B7" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137067756</v>
       </c>
       <c r="B8" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137067739</v>
       </c>
       <c r="B9" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>137067750</v>
       </c>
       <c r="B10" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>137067732</v>
       </c>
       <c r="B11" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>137067745</v>
       </c>
       <c r="B19" t="n">
-        <v>79178</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -1516,11 +1516,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skravelberget, Jmt</t>
@@ -1637,11 +1633,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skravelberget, Jmt</t>
@@ -1758,11 +1750,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skravelberget, Jmt</t>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137067742</v>
       </c>
       <c r="B2" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137129715</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>137129717</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137067746</v>
       </c>
       <c r="B6" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>456668</v>
       </c>
       <c r="R6" t="n">
-        <v>6956458</v>
+        <v>6956457</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1257,7 +1257,7 @@
         <v>137067755</v>
       </c>
       <c r="B7" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137067756</v>
       </c>
       <c r="B8" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137067739</v>
       </c>
       <c r="B9" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137067750</v>
       </c>
       <c r="B10" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>137067732</v>
       </c>
       <c r="B11" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>137067745</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>79190</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>456668</v>
       </c>
       <c r="R6" t="n">
-        <v>6956457</v>
+        <v>6956458</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1842,7 +1842,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137067742</v>
       </c>
       <c r="B2" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137129715</v>
       </c>
       <c r="B4" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>137129717</v>
       </c>
       <c r="B5" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137067746</v>
       </c>
       <c r="B6" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137067755</v>
       </c>
       <c r="B7" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137067756</v>
       </c>
       <c r="B8" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137067739</v>
       </c>
       <c r="B9" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137067750</v>
       </c>
       <c r="B10" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>137067732</v>
       </c>
       <c r="B11" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>137067745</v>
       </c>
       <c r="B19" t="n">
-        <v>79190</v>
+        <v>79193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137067742</v>
       </c>
       <c r="B2" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137129715</v>
       </c>
       <c r="B4" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>137129717</v>
       </c>
       <c r="B5" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137067746</v>
       </c>
       <c r="B6" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>456668</v>
       </c>
       <c r="R6" t="n">
-        <v>6956457</v>
+        <v>6956458</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1257,7 +1257,7 @@
         <v>137067755</v>
       </c>
       <c r="B7" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137067756</v>
       </c>
       <c r="B8" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137067739</v>
       </c>
       <c r="B9" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137067750</v>
       </c>
       <c r="B10" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>137067732</v>
       </c>
       <c r="B11" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>137067745</v>
       </c>
       <c r="B19" t="n">
-        <v>79193</v>
+        <v>79198</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -1180,7 +1180,7 @@
         <v>456668</v>
       </c>
       <c r="R6" t="n">
-        <v>6956458</v>
+        <v>6956457</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1842,7 +1842,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137067742</v>
       </c>
       <c r="B2" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137129715</v>
       </c>
       <c r="B4" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>137129717</v>
       </c>
       <c r="B5" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137067746</v>
       </c>
       <c r="B6" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>456668</v>
       </c>
       <c r="R6" t="n">
-        <v>6956457</v>
+        <v>6956458</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1257,7 +1257,7 @@
         <v>137067755</v>
       </c>
       <c r="B7" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137067756</v>
       </c>
       <c r="B8" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>137067745</v>
       </c>
       <c r="B19" t="n">
-        <v>79198</v>
+        <v>79209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137067742</v>
       </c>
       <c r="B2" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137129715</v>
       </c>
       <c r="B4" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>137129717</v>
       </c>
       <c r="B5" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137067746</v>
       </c>
       <c r="B6" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>456668</v>
       </c>
       <c r="R6" t="n">
-        <v>6956458</v>
+        <v>6956457</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1257,7 +1257,7 @@
         <v>137067755</v>
       </c>
       <c r="B7" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137067756</v>
       </c>
       <c r="B8" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>137067745</v>
       </c>
       <c r="B19" t="n">
-        <v>79209</v>
+        <v>79210</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137067742</v>
       </c>
       <c r="B2" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137129715</v>
       </c>
       <c r="B4" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>137129717</v>
       </c>
       <c r="B5" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137067746</v>
       </c>
       <c r="B6" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>456668</v>
       </c>
       <c r="R6" t="n">
-        <v>6956457</v>
+        <v>6956458</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1257,7 +1257,7 @@
         <v>137067755</v>
       </c>
       <c r="B7" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137067756</v>
       </c>
       <c r="B8" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>137067745</v>
       </c>
       <c r="B19" t="n">
-        <v>79210</v>
+        <v>79212</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39552-2026 artfynd.xlsx
+++ b/artfynd/A 39552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137067742</v>
       </c>
       <c r="B2" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137067749</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137129715</v>
       </c>
       <c r="B4" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>137129717</v>
       </c>
       <c r="B5" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137067746</v>
       </c>
       <c r="B6" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>456668</v>
       </c>
       <c r="R6" t="n">
-        <v>6956457</v>
+        <v>6956458</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1257,7 +1257,7 @@
         <v>137067755</v>
       </c>
       <c r="B7" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137067756</v>
       </c>
       <c r="B8" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137067739</v>
       </c>
       <c r="B9" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137067750</v>
       </c>
       <c r="B10" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>137067732</v>
       </c>
       <c r="B11" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137067737</v>
       </c>
       <c r="B12" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137067743</v>
       </c>
       <c r="B13" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>137067753</v>
       </c>
       <c r="B14" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137067735</v>
       </c>
       <c r="B15" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137067738</v>
       </c>
       <c r="B16" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>137067752</v>
       </c>
       <c r="B17" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137067760</v>
       </c>
       <c r="B18" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>137067745</v>
       </c>
       <c r="B19" t="n">
-        <v>79212</v>
+        <v>79216</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
